--- a/research/traditional_assets/database/data/chile/chile_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_insurance_general.xlsx
@@ -588,28 +588,28 @@
         </is>
       </c>
       <c r="E2">
-        <v>0.214</v>
+        <v>0.063</v>
       </c>
       <c r="K2">
-        <v>185.7</v>
+        <v>118.9</v>
       </c>
       <c r="M2">
-        <v>92.8058</v>
+        <v>68.80429999999998</v>
       </c>
       <c r="N2">
-        <v>0.1918664461443043</v>
+        <v>0.1222318351394564</v>
       </c>
       <c r="O2">
-        <v>0.4997619816908994</v>
+        <v>0.5786736753574431</v>
       </c>
       <c r="P2">
-        <v>92.8058</v>
+        <v>68.80429999999998</v>
       </c>
       <c r="Q2">
-        <v>0.1918664461443043</v>
+        <v>0.1222318351394564</v>
       </c>
       <c r="R2">
-        <v>0.4997619816908994</v>
+        <v>0.5786736753574431</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -618,67 +618,67 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>14.3</v>
+        <v>38.8</v>
       </c>
       <c r="V2">
-        <v>0.02956377920198471</v>
+        <v>0.06892876176940842</v>
       </c>
       <c r="W2">
-        <v>0.3358654367878459</v>
+        <v>0.2126251788268956</v>
       </c>
       <c r="X2">
-        <v>0.05330099486098252</v>
+        <v>0.08888979160033367</v>
       </c>
       <c r="Y2">
-        <v>0.2825644419268634</v>
+        <v>0.1237353872265619</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.001249406175771972</v>
+        <v>-0.00147212130785026</v>
       </c>
       <c r="AB2">
-        <v>0.04838321011003389</v>
+        <v>0.08386648024617689</v>
       </c>
       <c r="AC2">
-        <v>-0.04963261628580587</v>
+        <v>-0.08533860155402716</v>
       </c>
       <c r="AD2">
-        <v>88.2</v>
+        <v>84.7</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>88.2</v>
+        <v>84.7</v>
       </c>
       <c r="AG2">
-        <v>73.90000000000001</v>
+        <v>45.90000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.1542227662178703</v>
+        <v>0.1307906114885732</v>
       </c>
       <c r="AI2">
-        <v>0.1362372567191844</v>
+        <v>0.1263048016701461</v>
       </c>
       <c r="AJ2">
-        <v>0.132532281205165</v>
+        <v>0.07539421813403419</v>
       </c>
       <c r="AK2">
-        <v>0.1167272152898436</v>
+        <v>0.07264957264957267</v>
       </c>
       <c r="AL2">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="AM2">
-        <v>3.681</v>
+        <v>3.25</v>
       </c>
       <c r="AO2">
-        <v>-0.200253807106599</v>
+        <v>-0.2867692307692308</v>
       </c>
       <c r="AQ2">
-        <v>-0.2143439282803586</v>
+        <v>-0.2867692307692308</v>
       </c>
     </row>
     <row r="3">
@@ -698,28 +698,28 @@
         </is>
       </c>
       <c r="E3">
-        <v>0.214</v>
+        <v>0.063</v>
       </c>
       <c r="K3">
-        <v>185.7</v>
+        <v>118.9</v>
       </c>
       <c r="M3">
-        <v>92.8058</v>
+        <v>68.80429999999998</v>
       </c>
       <c r="N3">
-        <v>0.1918664461443043</v>
+        <v>0.1222318351394564</v>
       </c>
       <c r="O3">
-        <v>0.4997619816908994</v>
+        <v>0.5786736753574431</v>
       </c>
       <c r="P3">
-        <v>92.8058</v>
+        <v>68.80429999999998</v>
       </c>
       <c r="Q3">
-        <v>0.1918664461443043</v>
+        <v>0.1222318351394564</v>
       </c>
       <c r="R3">
-        <v>0.4997619816908994</v>
+        <v>0.5786736753574431</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -728,67 +728,67 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>14.3</v>
+        <v>38.8</v>
       </c>
       <c r="V3">
-        <v>0.02956377920198471</v>
+        <v>0.06892876176940842</v>
       </c>
       <c r="W3">
-        <v>0.3358654367878459</v>
+        <v>0.2126251788268956</v>
       </c>
       <c r="X3">
-        <v>0.05330099486098252</v>
+        <v>0.08888979160033367</v>
       </c>
       <c r="Y3">
-        <v>0.2825644419268634</v>
+        <v>0.1237353872265619</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.001249406175771972</v>
+        <v>-0.00147212130785026</v>
       </c>
       <c r="AB3">
-        <v>0.04838321011003389</v>
+        <v>0.08386648024617689</v>
       </c>
       <c r="AC3">
-        <v>-0.04963261628580587</v>
+        <v>-0.08533860155402716</v>
       </c>
       <c r="AD3">
-        <v>88.2</v>
+        <v>84.7</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>88.2</v>
+        <v>84.7</v>
       </c>
       <c r="AG3">
-        <v>73.90000000000001</v>
+        <v>45.90000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.1542227662178703</v>
+        <v>0.1307906114885732</v>
       </c>
       <c r="AI3">
-        <v>0.1362372567191844</v>
+        <v>0.1263048016701461</v>
       </c>
       <c r="AJ3">
-        <v>0.132532281205165</v>
+        <v>0.07539421813403419</v>
       </c>
       <c r="AK3">
-        <v>0.1167272152898436</v>
+        <v>0.07264957264957267</v>
       </c>
       <c r="AL3">
-        <v>3.94</v>
+        <v>3.25</v>
       </c>
       <c r="AM3">
-        <v>3.681</v>
+        <v>3.25</v>
       </c>
       <c r="AO3">
-        <v>-0.200253807106599</v>
+        <v>-0.2867692307692308</v>
       </c>
       <c r="AQ3">
-        <v>-0.2143439282803586</v>
+        <v>-0.2867692307692308</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/chile/chile_insurance_general.xlsx
+++ b/research/traditional_assets/database/data/chile/chile_insurance_general.xlsx
@@ -588,97 +588,94 @@
         </is>
       </c>
       <c r="E2">
-        <v>0.063</v>
+        <v>0.175</v>
       </c>
       <c r="K2">
-        <v>118.9</v>
+        <v>108.8</v>
       </c>
       <c r="M2">
-        <v>68.80429999999998</v>
+        <v>0</v>
       </c>
       <c r="N2">
-        <v>0.1222318351394564</v>
+        <v>0</v>
       </c>
       <c r="O2">
-        <v>0.5786736753574431</v>
+        <v>0</v>
       </c>
       <c r="P2">
-        <v>68.80429999999998</v>
+        <v>0</v>
       </c>
       <c r="Q2">
-        <v>0.1222318351394564</v>
+        <v>0</v>
       </c>
       <c r="R2">
-        <v>0.5786736753574431</v>
+        <v>0</v>
       </c>
       <c r="S2">
         <v>0</v>
       </c>
-      <c r="T2">
-        <v>0</v>
-      </c>
       <c r="U2">
-        <v>38.8</v>
+        <v>18.4</v>
       </c>
       <c r="V2">
-        <v>0.06892876176940842</v>
+        <v>0.0264026402640264</v>
       </c>
       <c r="W2">
-        <v>0.2126251788268956</v>
+        <v>0.1856972179552825</v>
       </c>
       <c r="X2">
-        <v>0.08888979160033367</v>
+        <v>0.07880323885935361</v>
       </c>
       <c r="Y2">
-        <v>0.1237353872265619</v>
+        <v>0.1068939790959288</v>
       </c>
       <c r="Z2">
         <v>0</v>
       </c>
       <c r="AA2">
-        <v>-0.00147212130785026</v>
+        <v>-0.0008257203243390806</v>
       </c>
       <c r="AB2">
-        <v>0.08386648024617689</v>
+        <v>0.07479672533446578</v>
       </c>
       <c r="AC2">
-        <v>-0.08533860155402716</v>
+        <v>-0.07562244565880487</v>
       </c>
       <c r="AD2">
-        <v>84.7</v>
+        <v>96.3</v>
       </c>
       <c r="AE2">
         <v>0</v>
       </c>
       <c r="AF2">
-        <v>84.7</v>
+        <v>96.3</v>
       </c>
       <c r="AG2">
-        <v>45.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AH2">
-        <v>0.1307906114885732</v>
+        <v>0.1214069591527988</v>
       </c>
       <c r="AI2">
-        <v>0.1263048016701461</v>
+        <v>0.1330110497237569</v>
       </c>
       <c r="AJ2">
-        <v>0.07539421813403419</v>
+        <v>0.1005420753742901</v>
       </c>
       <c r="AK2">
-        <v>0.07264957264957267</v>
+        <v>0.1104024943310658</v>
       </c>
       <c r="AL2">
-        <v>3.25</v>
+        <v>4.09</v>
       </c>
       <c r="AM2">
-        <v>3.25</v>
+        <v>4.09</v>
       </c>
       <c r="AO2">
-        <v>-0.2867692307692308</v>
+        <v>-0.1278728606356968</v>
       </c>
       <c r="AQ2">
-        <v>-0.2867692307692308</v>
+        <v>-0.1278728606356968</v>
       </c>
     </row>
     <row r="3">
@@ -698,97 +695,94 @@
         </is>
       </c>
       <c r="E3">
-        <v>0.063</v>
+        <v>0.175</v>
       </c>
       <c r="K3">
-        <v>118.9</v>
+        <v>108.8</v>
       </c>
       <c r="M3">
-        <v>68.80429999999998</v>
+        <v>-0</v>
       </c>
       <c r="N3">
-        <v>0.1222318351394564</v>
+        <v>-0</v>
       </c>
       <c r="O3">
-        <v>0.5786736753574431</v>
+        <v>-0</v>
       </c>
       <c r="P3">
-        <v>68.80429999999998</v>
+        <v>-0</v>
       </c>
       <c r="Q3">
-        <v>0.1222318351394564</v>
+        <v>-0</v>
       </c>
       <c r="R3">
-        <v>0.5786736753574431</v>
+        <v>-0</v>
       </c>
       <c r="S3">
         <v>0</v>
       </c>
-      <c r="T3">
-        <v>0</v>
-      </c>
       <c r="U3">
-        <v>38.8</v>
+        <v>18.4</v>
       </c>
       <c r="V3">
-        <v>0.06892876176940842</v>
+        <v>0.0264026402640264</v>
       </c>
       <c r="W3">
-        <v>0.2126251788268956</v>
+        <v>0.1856972179552825</v>
       </c>
       <c r="X3">
-        <v>0.08888979160033367</v>
+        <v>0.07880323885935361</v>
       </c>
       <c r="Y3">
-        <v>0.1237353872265619</v>
+        <v>0.1068939790959288</v>
       </c>
       <c r="Z3">
         <v>0</v>
       </c>
       <c r="AA3">
-        <v>-0.00147212130785026</v>
+        <v>-0.0008257203243390806</v>
       </c>
       <c r="AB3">
-        <v>0.08386648024617689</v>
+        <v>0.07479672533446578</v>
       </c>
       <c r="AC3">
-        <v>-0.08533860155402716</v>
+        <v>-0.07562244565880487</v>
       </c>
       <c r="AD3">
-        <v>84.7</v>
+        <v>96.3</v>
       </c>
       <c r="AE3">
         <v>0</v>
       </c>
       <c r="AF3">
-        <v>84.7</v>
+        <v>96.3</v>
       </c>
       <c r="AG3">
-        <v>45.90000000000001</v>
+        <v>77.90000000000001</v>
       </c>
       <c r="AH3">
-        <v>0.1307906114885732</v>
+        <v>0.1214069591527988</v>
       </c>
       <c r="AI3">
-        <v>0.1263048016701461</v>
+        <v>0.1330110497237569</v>
       </c>
       <c r="AJ3">
-        <v>0.07539421813403419</v>
+        <v>0.1005420753742901</v>
       </c>
       <c r="AK3">
-        <v>0.07264957264957267</v>
+        <v>0.1104024943310658</v>
       </c>
       <c r="AL3">
-        <v>3.25</v>
+        <v>4.09</v>
       </c>
       <c r="AM3">
-        <v>3.25</v>
+        <v>4.09</v>
       </c>
       <c r="AO3">
-        <v>-0.2867692307692308</v>
+        <v>-0.1278728606356968</v>
       </c>
       <c r="AQ3">
-        <v>-0.2867692307692308</v>
+        <v>-0.1278728606356968</v>
       </c>
     </row>
   </sheetData>
